--- a/Result/profitability/2867.xlsx
+++ b/Result/profitability/2867.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
         <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09250000000000011</v>
+        <v>0.2925000000000001</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -778,7 +778,7 @@
         <v>2.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4725000000000001</v>
+        <v>0.5975000000000001</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -895,7 +895,7 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3987500000000001</v>
+        <v>0.5075000000000001</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -1012,7 +1012,7 @@
         <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4075000000000001</v>
+        <v>0.5387500000000001</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1129,7 +1129,7 @@
         <v>0.82</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5287500000000001</v>
+        <v>0.6062500000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1254,7 +1254,7 @@
         <v>1.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6900000000000001</v>
+        <v>0.7975000000000001</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1379,7 +1379,7 @@
         <v>-0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6512500000000001</v>
+        <v>0.7675000000000001</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -1504,7 +1504,7 @@
         <v>0.08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6650000000000001</v>
+        <v>0.665</v>
       </c>
       <c r="N9" t="n">
         <v>4.3775</v>
@@ -9655,6 +9655,119 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2867</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>7051</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>86.23%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>-1063</v>
+      </c>
+      <c r="J74" t="n">
+        <v>5988</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5286</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.0337500000000001</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-31</v>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="n">
+        <v>0.02162162162162162</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
